--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>7.188281030107957</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>6.318086881568341</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>7.549913043478251</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>3.075199146932706</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>6.182948115694153</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>5.803374136298278</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>4.661589226330687</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>5.76000000000001</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>4.621379464396513</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>8.775104214368245</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>3.53436749375835</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>5.142121212121209</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>8.394442664052626</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>3.909187655196877</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>6.80323741912745</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>7.976340120341252</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>5.424312499999995</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>6.159365079365076</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>9.222573795307376</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>4.707043483212181</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>5.824039653035928</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>7.289640181682389</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>9.307246620203212</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>7.857873873873866</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>6.857274348501408</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>7.035557939292025</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>6.263651075268051</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>6.976107476095028</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>6.779591139590901</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1042,9 +950,6 @@
       </c>
       <c r="E31">
         <v>8.496694000456007</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -613,342 +613,361 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B14">
-        <v>862500</v>
+        <v>866220</v>
       </c>
       <c r="C14">
-        <v>795705</v>
+        <v>817903</v>
       </c>
       <c r="D14">
-        <v>66795</v>
+        <v>48317</v>
       </c>
       <c r="E14">
-        <v>8.394442664052626</v>
+        <v>5.907424230012603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="B15">
-        <v>849468</v>
+        <v>862500</v>
       </c>
       <c r="C15">
-        <v>817510</v>
+        <v>795705</v>
       </c>
       <c r="D15">
-        <v>31958</v>
+        <v>66795</v>
       </c>
       <c r="E15">
-        <v>3.909187655196877</v>
+        <v>8.394442664052626</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="B16">
-        <v>848509</v>
+        <v>849468</v>
       </c>
       <c r="C16">
-        <v>794460</v>
+        <v>817510</v>
       </c>
       <c r="D16">
-        <v>54049</v>
+        <v>31958</v>
       </c>
       <c r="E16">
-        <v>6.80323741912745</v>
+        <v>3.909187655196877</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="B17">
-        <v>846108</v>
+        <v>848509</v>
       </c>
       <c r="C17">
-        <v>783605</v>
+        <v>794460</v>
       </c>
       <c r="D17">
-        <v>62503</v>
+        <v>54049</v>
       </c>
       <c r="E17">
-        <v>7.976340120341252</v>
+        <v>6.80323741912745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="B18">
-        <v>843394.5</v>
+        <v>846108</v>
       </c>
       <c r="C18">
-        <v>800000</v>
+        <v>783605</v>
       </c>
       <c r="D18">
-        <v>43394.5</v>
+        <v>62503</v>
       </c>
       <c r="E18">
-        <v>5.424312499999995</v>
+        <v>7.976340120341252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="B19">
-        <v>836005</v>
+        <v>843394.5</v>
       </c>
       <c r="C19">
-        <v>787500</v>
+        <v>800000</v>
       </c>
       <c r="D19">
-        <v>48505</v>
+        <v>43394.5</v>
       </c>
       <c r="E19">
-        <v>6.159365079365076</v>
+        <v>5.424312499999995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="B20">
-        <v>831210</v>
+        <v>836005</v>
       </c>
       <c r="C20">
-        <v>761024</v>
+        <v>787500</v>
       </c>
       <c r="D20">
-        <v>70186</v>
+        <v>48505</v>
       </c>
       <c r="E20">
-        <v>9.222573795307376</v>
+        <v>6.159365079365076</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="B21">
-        <v>827505</v>
+        <v>831210</v>
       </c>
       <c r="C21">
-        <v>790305</v>
+        <v>761024</v>
       </c>
       <c r="D21">
-        <v>37200</v>
+        <v>70186</v>
       </c>
       <c r="E21">
-        <v>4.707043483212181</v>
+        <v>9.222573795307376</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="B22">
-        <v>819840</v>
+        <v>827505</v>
       </c>
       <c r="C22">
-        <v>774720</v>
+        <v>790305</v>
       </c>
       <c r="D22">
-        <v>45120</v>
+        <v>37200</v>
       </c>
       <c r="E22">
-        <v>5.824039653035928</v>
+        <v>4.707043483212181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="B23">
-        <v>785056</v>
+        <v>819840</v>
       </c>
       <c r="C23">
-        <v>731716.5</v>
+        <v>774720</v>
       </c>
       <c r="D23">
-        <v>53339.5</v>
+        <v>45120</v>
       </c>
       <c r="E23">
-        <v>7.289640181682389</v>
+        <v>5.824039653035928</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="B24">
-        <v>781044</v>
+        <v>785056</v>
       </c>
       <c r="C24">
-        <v>714540</v>
+        <v>731716.5</v>
       </c>
       <c r="D24">
-        <v>66504</v>
+        <v>53339.5</v>
       </c>
       <c r="E24">
-        <v>9.307246620203212</v>
+        <v>7.289640181682389</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="B25">
-        <v>748264</v>
+        <v>781044</v>
       </c>
       <c r="C25">
-        <v>693750</v>
+        <v>714540</v>
       </c>
       <c r="D25">
-        <v>54514</v>
+        <v>66504</v>
       </c>
       <c r="E25">
-        <v>7.857873873873866</v>
+        <v>9.307246620203212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="B26">
-        <v>743000</v>
+        <v>748264</v>
       </c>
       <c r="C26">
-        <v>695320</v>
+        <v>693750</v>
       </c>
       <c r="D26">
-        <v>47680</v>
+        <v>54514</v>
       </c>
       <c r="E26">
-        <v>6.857274348501408</v>
+        <v>7.857873873873866</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="B27">
-        <v>738395.5</v>
+        <v>743000</v>
       </c>
       <c r="C27">
-        <v>689860</v>
+        <v>695320</v>
       </c>
       <c r="D27">
-        <v>48535.5</v>
+        <v>47680</v>
       </c>
       <c r="E27">
-        <v>7.035557939292025</v>
+        <v>6.857274348501408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="B28">
-        <v>736100</v>
+        <v>738395.5</v>
       </c>
       <c r="C28">
-        <v>692711</v>
+        <v>689860</v>
       </c>
       <c r="D28">
-        <v>43389</v>
+        <v>48535.5</v>
       </c>
       <c r="E28">
-        <v>6.263651075268051</v>
+        <v>7.035557939292025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="B29">
-        <v>730665</v>
+        <v>736100</v>
       </c>
       <c r="C29">
-        <v>683017</v>
+        <v>692711</v>
       </c>
       <c r="D29">
-        <v>47648</v>
+        <v>43389</v>
       </c>
       <c r="E29">
-        <v>6.976107476095028</v>
+        <v>6.263651075268051</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="B30">
-        <v>725200</v>
+        <v>730665</v>
       </c>
       <c r="C30">
-        <v>679156</v>
+        <v>683017</v>
       </c>
       <c r="D30">
-        <v>46044</v>
+        <v>47648</v>
       </c>
       <c r="E30">
-        <v>6.779591139590901</v>
+        <v>6.976107476095028</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>725200</v>
+      </c>
+      <c r="C31">
+        <v>679156</v>
+      </c>
+      <c r="D31">
+        <v>46044</v>
+      </c>
+      <c r="E31">
+        <v>6.779591139590901</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>690001</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>635965</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>54036</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>8.496694000456007</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_los_lagos.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>862500</v>
+          <t>San Pablo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>906409.5</v>
+          <t>Puqueldón</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>892350</v>
+          <t>Fresia</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>927618</v>
+          <t>Llanquihue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>849468</v>
+          <t>Osorno</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>885213</v>
+          <t>Purranque</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>836005</v>
+          <t>Puyehue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>819840</v>
+          <t>Cochamó</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>725200</v>
+          <t>Ancud</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>781044</v>
+          <t>Quellón</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>876500</v>
+          <t>Queilén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>962083</v>
+          <t>Chonchi</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>827505</v>
+          <t>Puerto Montt</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>736100</v>
+          <t>Río Negro</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>831210</v>
+          <t>Castro</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>846108</v>
+          <t>Dalcahue</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>904968</v>
+          <t>Quemchi</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>893507.5</v>
+          <t>San Juan de la Costa</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>785056</v>
+          <t>Calbuco</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>1013000</v>
+          <t>Chaitén</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>867422.5</v>
+          <t>Los Muermos</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>748264</v>
+          <t>Maullín</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>730665</v>
+          <t>Quinchao</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>843394.5</v>
+          <t>Curaco de Vélez</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>912500</v>
+          <t>Puerto Octay</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>875000</v>
+          <t>Frutillar</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>848509</v>
+          <t>Puerto Varas</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>738395.5</v>
+          <t>Hualaihué</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>690001</v>
+          <t>Palena</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>743000</v>
+          <t>Futaleufú</t>
+        </is>
       </c>
     </row>
   </sheetData>
